--- a/data/trans_orig/P16A_n_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de medicamentos consumidos por persona en las dos últimas semanas</t>
+          <t>Población según número de medicamentos consumidos por persona en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,27 +721,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,4</t>
+          <t>0,29; 0,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,33</t>
+          <t>0,21; 0,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,45</t>
+          <t>0,24; 0,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,6</t>
+          <t>0,45; 0,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,8</t>
+          <t>0,62; 0,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,76</t>
+          <t>0,45; 0,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -861,32 +861,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,67</t>
+          <t>0,43; 0,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,49</t>
+          <t>0,37; 0,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,58</t>
+          <t>0,39; 0,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,71</t>
+          <t>0,56; 0,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 0,96</t>
+          <t>0,79; 0,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,76</t>
+          <t>0,62; 0,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,22 +896,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,47</t>
+          <t>0,39; 0,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,76</t>
+          <t>0,62; 0,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,6</t>
+          <t>0,51; 0,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,74</t>
+          <t>0,56; 0,73</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,65</t>
+          <t>0,5; 0,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,32 +1011,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,76</t>
+          <t>0,55; 0,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,78</t>
+          <t>0,62; 0,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,16</t>
+          <t>0,94; 1,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 0,85</t>
+          <t>0,7; 0,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,92</t>
+          <t>0,59; 0,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,61</t>
+          <t>0,5; 0,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,69</t>
+          <t>0,59; 0,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,81</t>
+          <t>0,63; 0,8</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,77</t>
+          <t>0,56; 0,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,93</t>
+          <t>0,71; 0,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,21</t>
+          <t>0,37; 1,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,22 +1161,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,48</t>
+          <t>1,24; 1,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,26</t>
+          <t>1,02; 1,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,5</t>
+          <t>1,14; 1,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 0,89</t>
+          <t>0,74; 0,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,04</t>
+          <t>0,9; 1,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,3</t>
+          <t>0,67; 1,31</t>
         </is>
       </c>
     </row>
@@ -1276,47 +1276,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,44</t>
+          <t>1,2; 1,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,61</t>
+          <t>1,36; 1,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,46</t>
+          <t>1,18; 1,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,8</t>
+          <t>1,54; 1,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 1,79</t>
+          <t>1,49; 1,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 2,36</t>
+          <t>2,0; 2,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,12</t>
+          <t>1,78; 2,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 2,26</t>
+          <t>1,99; 2,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,57</t>
+          <t>1,38; 1,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,75</t>
+          <t>1,52; 1,74</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 1,99</t>
+          <t>1,8; 1,99</t>
         </is>
       </c>
     </row>
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 1,82</t>
+          <t>1,48; 1,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 2,56</t>
+          <t>2,13; 2,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,1</t>
+          <t>1,76; 2,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 2,3</t>
+          <t>1,98; 2,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 2,44</t>
+          <t>2,09; 2,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 3,11</t>
+          <t>2,66; 3,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,68</t>
+          <t>2,76; 3,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 2,1</t>
+          <t>1,85; 2,09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 2,79</t>
+          <t>2,48; 2,79</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 2,35</t>
+          <t>2,1; 2,36</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 3,36</t>
+          <t>2,46; 3,37</t>
         </is>
       </c>
     </row>
@@ -1556,37 +1556,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,07; 2,51</t>
+          <t>2,06; 2,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,21</t>
+          <t>2,72; 3,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 2,67</t>
+          <t>2,32; 2,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 3,21</t>
+          <t>2,8; 3,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 2,6</t>
+          <t>2,25; 2,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,34; 3,75</t>
+          <t>3,32; 3,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,15</t>
+          <t>2,75; 3,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 2,51</t>
+          <t>2,22; 2,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,15; 3,46</t>
+          <t>3,16; 3,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 3,71</t>
+          <t>3,43; 3,72</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 0,75</t>
+          <t>0,68; 0,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1706,17 +1706,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 0,96</t>
+          <t>0,87; 0,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,27</t>
+          <t>0,89; 1,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,19</t>
+          <t>1,1; 1,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,45</t>
+          <t>1,34; 1,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,25</t>
+          <t>1,69; 2,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,36</t>
+          <t>1,29; 1,37</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,75</t>
+          <t>1,38; 1,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,47</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,41</t>
+          <t>0,28; 0,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,34</t>
+          <t>0,22; 0,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,46</t>
+          <t>0,25; 0,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,78</t>
+          <t>0,62; 0,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,76</t>
+          <t>0,49; 0,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,57</t>
+          <t>0,47; 0,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,55</t>
+          <t>0,39; 0,58</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,59</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,65</t>
+          <t>0,43; 0,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,5</t>
+          <t>0,37; 0,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -881,17 +881,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 0,97</t>
+          <t>0,8; 0,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,78</t>
+          <t>0,62; 0,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,88</t>
+          <t>0,6; 0,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,77</t>
+          <t>0,62; 0,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,61</t>
+          <t>0,5; 0,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,73</t>
+          <t>0,53; 0,66</t>
         </is>
       </c>
     </row>
@@ -943,47 +943,47 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>0,6</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,69</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,04</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0,78</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0,88</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0,56</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0,81</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>0,63</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,04</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,56</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,74</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,65</t>
+          <t>0,5; 0,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,56</t>
+          <t>0,43; 0,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,75</t>
+          <t>0,52; 0,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,93</t>
+          <t>0,8; 0,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,6</t>
+          <t>0,5; 0,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,8</t>
+          <t>0,68; 0,81</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,26</t>
         </is>
       </c>
     </row>
@@ -1136,22 +1136,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,76</t>
+          <t>0,56; 0,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 0,92</t>
+          <t>0,72; 0,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,89</t>
+          <t>0,73; 0,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,22</t>
+          <t>1,02; 1,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1166,17 +1166,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,25</t>
+          <t>1,03; 1,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,5</t>
+          <t>1,27; 1,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 0,9</t>
+          <t>0,73; 0,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,04</t>
+          <t>0,91; 1,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,31</t>
+          <t>1,17; 1,36</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>1,88</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,45</t>
+          <t>1,19; 1,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,62</t>
+          <t>1,36; 1,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,47 +1291,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 1,81</t>
+          <t>1,5; 1,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 1,8</t>
+          <t>1,48; 1,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 2,38</t>
+          <t>2,0; 2,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,08</t>
+          <t>1,78; 2,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 2,27</t>
+          <t>2,01; 2,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,58</t>
+          <t>1,38; 1,57</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 1,95</t>
+          <t>1,72; 1,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,74</t>
+          <t>1,52; 1,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 1,99</t>
+          <t>1,79; 1,97</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,22</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>2,49</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 1,83</t>
+          <t>1,46; 1,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,13; 2,57</t>
+          <t>2,14; 2,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,1</t>
+          <t>1,75; 2,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 2,31</t>
+          <t>1,93; 2,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 2,43</t>
+          <t>2,08; 2,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 3,13</t>
+          <t>2,68; 3,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 2,7</t>
+          <t>2,28; 2,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,63</t>
+          <t>2,69; 3,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 2,09</t>
+          <t>1,84; 2,09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,48; 2,79</t>
+          <t>2,48; 2,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 2,36</t>
+          <t>2,1; 2,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,46; 3,37</t>
+          <t>2,38; 2,6</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,99</t>
+          <t>2,98</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,94</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,56</t>
+          <t>3,55</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 2,49</t>
+          <t>2,05; 2,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1566,52 +1566,52 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 2,68</t>
+          <t>2,33; 2,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 3,22</t>
+          <t>2,76; 3,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 2,61</t>
+          <t>2,24; 2,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,32; 3,76</t>
+          <t>3,34; 3,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 3,14</t>
+          <t>2,75; 3,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,76; 4,12</t>
+          <t>3,73; 4,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 2,49</t>
+          <t>2,23; 2,51</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,16; 3,46</t>
+          <t>3,14; 3,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 2,92</t>
+          <t>2,63; 2,91</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 3,72</t>
+          <t>3,4; 3,7</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,49</t>
         </is>
       </c>
     </row>
@@ -1701,22 +1701,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,07</t>
+          <t>0,97; 1,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,87; 0,96</t>
+          <t>0,88; 0,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,26</t>
+          <t>1,17; 1,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,19</t>
+          <t>1,1; 1,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,24</t>
+          <t>1,69; 1,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,37</t>
+          <t>1,28; 1,37</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,71</t>
+          <t>1,44; 1,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de medicamentos consumidos por persona en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
+          <t>Población según el número de medicamentos consumidos por persona en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
